--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ARIZONA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ARIZONA_2018.xlsx
@@ -1957,7 +1957,7 @@
         <v>104</v>
       </c>
       <c r="D89">
-        <v>0.009553555024802499</v>
+        <v>0.0095535550248025</v>
       </c>
     </row>
     <row r="90">
@@ -3451,7 +3451,7 @@
         <v>104</v>
       </c>
       <c r="D172">
-        <v>0.009553555024802499</v>
+        <v>0.0095535550248025</v>
       </c>
     </row>
     <row r="173">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C284">
@@ -17473,7 +17473,7 @@
         <v>100</v>
       </c>
       <c r="D951">
-        <v>0.009186110600771633</v>
+        <v>0.009186110600771631</v>
       </c>
     </row>
     <row r="952">
